--- a/data/trans_dic/P17G_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico de la seguridad social en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a de la seguridad social (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,14; 86,88</t>
+          <t>63,3; 85,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,4; 100,0</t>
+          <t>89,89; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,33; 86,3</t>
+          <t>63,35; 85,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80,23; 97,35</t>
+          <t>81,2; 96,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,2; 95,73</t>
+          <t>80,56; 95,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,46; 100,0</t>
+          <t>92,75; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,96; 97,02</t>
+          <t>86,36; 97,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,45; 92,98</t>
+          <t>81,44; 93,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>75,24; 89,57</t>
+          <t>76,88; 90,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93,99; 99,36</t>
+          <t>94,2; 99,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79,51; 91,17</t>
+          <t>79,42; 90,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,66; 93,49</t>
+          <t>84,16; 93,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,41; 96,6</t>
+          <t>82,48; 96,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,56; 96,36</t>
+          <t>82,25; 96,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,62; 99,01</t>
+          <t>88,62; 99,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,07; 95,99</t>
+          <t>81,39; 95,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,7; 94,71</t>
+          <t>84,39; 95,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,62; 97,99</t>
+          <t>90,17; 98,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,57; 98,79</t>
+          <t>93,12; 98,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,59; 96,15</t>
+          <t>85,1; 95,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,66; 94,7</t>
+          <t>86,11; 94,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89,57; 96,46</t>
+          <t>89,11; 96,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92,7; 97,91</t>
+          <t>92,62; 97,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>85,87; 94,74</t>
+          <t>85,95; 94,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,27; 98,27</t>
+          <t>82,77; 98,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,67; 97,71</t>
+          <t>86,7; 97,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,97; 95,38</t>
+          <t>81,6; 95,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80,74; 96,52</t>
+          <t>80,65; 96,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,43; 99,04</t>
+          <t>90,5; 99,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,37; 99,28</t>
+          <t>90,34; 99,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,68; 97,83</t>
+          <t>89,13; 98,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,73; 95,56</t>
+          <t>84,66; 95,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,52; 98,2</t>
+          <t>90,39; 97,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,66; 97,94</t>
+          <t>91,84; 97,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88,44; 95,88</t>
+          <t>88,38; 95,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85,78; 94,5</t>
+          <t>86,44; 94,7</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,12; 98,35</t>
+          <t>85,81; 98,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,6; 95,73</t>
+          <t>77,44; 95,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,79; 98,85</t>
+          <t>87,34; 98,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79,54; 95,23</t>
+          <t>79,17; 95,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,59; 97,67</t>
+          <t>89,11; 97,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,12; 99,13</t>
+          <t>92,33; 99,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,74; 94,69</t>
+          <t>82,37; 94,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>88,48; 98,68</t>
+          <t>88,24; 98,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,36; 97,29</t>
+          <t>90,67; 97,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88,51; 96,78</t>
+          <t>88,48; 96,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86,8; 95,49</t>
+          <t>86,5; 95,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,71; 97,15</t>
+          <t>87,87; 97,39</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>81,54; 97,87</t>
+          <t>81,59; 97,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,13; 96,42</t>
+          <t>77,75; 96,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64,69; 96,34</t>
+          <t>62,43; 96,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,07; 100,0</t>
+          <t>77,89; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,67; 97,91</t>
+          <t>84,74; 98,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,82; 96,9</t>
+          <t>86,67; 97,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,09; 100,0</t>
+          <t>86,87; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,11; 93,73</t>
+          <t>73,11; 93,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86,34; 96,71</t>
+          <t>86,28; 96,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86,16; 95,78</t>
+          <t>86,56; 95,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83,52; 96,57</t>
+          <t>82,32; 96,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,94; 94,34</t>
+          <t>78,69; 94,38</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>81,58; 97,95</t>
+          <t>81,11; 97,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97,48; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,97; 100,0</t>
+          <t>94,08; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92,2; 99,16</t>
+          <t>93,24; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>89,83; 98,9</t>
+          <t>89,77; 98,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>98,12; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,18; 99,23</t>
+          <t>92,33; 99,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>85,55; 97,0</t>
+          <t>87,31; 97,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89,21; 97,28</t>
+          <t>89,42; 97,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>98,92; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94,75; 98,79</t>
+          <t>94,77; 99,11</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>90,57; 97,49</t>
+          <t>90,83; 97,62</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>87,47; 96,22</t>
+          <t>87,89; 96,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,81; 95,26</t>
+          <t>86,53; 95,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,82; 97,21</t>
+          <t>87,96; 97,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73,84; 89,01</t>
+          <t>74,17; 89,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,24; 96,94</t>
+          <t>90,09; 96,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,75; 96,28</t>
+          <t>88,54; 96,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,38; 97,47</t>
+          <t>90,73; 97,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>77,38; 87,51</t>
+          <t>77,76; 87,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>90,78; 96,08</t>
+          <t>90,57; 96,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89,38; 94,95</t>
+          <t>89,68; 95,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91,11; 96,47</t>
+          <t>90,89; 96,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,23; 86,4</t>
+          <t>77,8; 86,71</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>84,13; 93,74</t>
+          <t>83,65; 93,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88,46; 97,21</t>
+          <t>88,4; 97,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,08; 92,59</t>
+          <t>84,48; 92,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86,28; 95,56</t>
+          <t>86,67; 95,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,11; 96,64</t>
+          <t>90,5; 96,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,93; 98,55</t>
+          <t>92,74; 98,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,34; 94,78</t>
+          <t>87,47; 94,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,66; 96,33</t>
+          <t>90,01; 96,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>89,22; 94,68</t>
+          <t>89,4; 94,69</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92,08; 97,21</t>
+          <t>92,44; 97,24</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87,61; 93,1</t>
+          <t>87,67; 93,33</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>89,87; 95,1</t>
+          <t>90,07; 94,98</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>88,23; 92,74</t>
+          <t>87,9; 92,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>91,07; 95,09</t>
+          <t>91,05; 94,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89,0; 93,06</t>
+          <t>89,31; 93,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87,11; 92,11</t>
+          <t>86,85; 92,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>92,25; 95,2</t>
+          <t>91,97; 95,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>94,61; 97,07</t>
+          <t>94,5; 97,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>92,2; 95,22</t>
+          <t>92,14; 95,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>88,42; 92,64</t>
+          <t>88,34; 92,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>91,25; 93,91</t>
+          <t>91,11; 93,78</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93,64; 95,83</t>
+          <t>93,64; 95,81</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91,45; 93,92</t>
+          <t>91,38; 93,86</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>88,47; 91,88</t>
+          <t>88,34; 91,69</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico de la seguridad social en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a de la seguridad social (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31195; 42929</t>
+          <t>31274; 42425</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55837; 61764</t>
+          <t>55522; 61764</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44223; 59324</t>
+          <t>43551; 58942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56319; 68332</t>
+          <t>56999; 68049</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52422; 63365</t>
+          <t>53326; 63115</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88561; 94762</t>
+          <t>87892; 94762</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81481; 90911</t>
+          <t>80915; 90975</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61298; 69974</t>
+          <t>61287; 70136</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>86983; 103548</t>
+          <t>88870; 104318</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>147117; 155525</t>
+          <t>147440; 155548</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129168; 148104</t>
+          <t>129015; 147743</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>121691; 135978</t>
+          <t>122409; 136039</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73398; 86038</t>
+          <t>73458; 85997</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85632; 99950</t>
+          <t>85310; 100547</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96068; 108561</t>
+          <t>97172; 108574</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67493; 78941</t>
+          <t>66937; 78767</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>112023; 125260</t>
+          <t>111605; 125990</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>140851; 152294</t>
+          <t>140150; 152331</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>166340; 177521</t>
+          <t>167324; 177537</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82728; 92936</t>
+          <t>82247; 92325</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>191785; 209578</t>
+          <t>190565; 209094</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>232127; 249976</t>
+          <t>230912; 249864</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>268219; 283283</t>
+          <t>267981; 283348</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>153621; 169489</t>
+          <t>153765; 169375</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44328; 53600</t>
+          <t>45144; 53582</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70375; 78433</t>
+          <t>69590; 78459</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59452; 69181</t>
+          <t>59186; 69314</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51110; 61105</t>
+          <t>51053; 61007</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>91903; 99552</t>
+          <t>90966; 99516</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>125737; 138135</t>
+          <t>125697; 138134</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90908; 100284</t>
+          <t>91367; 100575</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64206; 72416</t>
+          <t>64154; 72119</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>140356; 152265</t>
+          <t>140150; 151742</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>201106; 214886</t>
+          <t>201490; 214956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154807; 167826</t>
+          <t>154693; 167801</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>119303; 131430</t>
+          <t>120233; 131710</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44836; 50615</t>
+          <t>44164; 50617</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54953; 66923</t>
+          <t>54138; 66856</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76882; 86561</t>
+          <t>76480; 86551</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55886; 66910</t>
+          <t>55631; 66786</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>107438; 117130</t>
+          <t>106858; 117091</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>101012; 108704</t>
+          <t>101249; 108704</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>111017; 127059</t>
+          <t>110522; 126178</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>150272; 167607</t>
+          <t>149880; 167274</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>154859; 166744</t>
+          <t>155394; 166660</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>158930; 173779</t>
+          <t>158873; 173731</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>192488; 211751</t>
+          <t>191811; 210955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>210595; 233273</t>
+          <t>210989; 233841</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36464; 43761</t>
+          <t>36486; 43785</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40621; 50130</t>
+          <t>40422; 50107</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18874; 28109</t>
+          <t>18215; 28153</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13877; 18243</t>
+          <t>14210; 18243</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>64450; 74528</t>
+          <t>64509; 75041</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79045; 88221</t>
+          <t>78903; 89047</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44680; 50720</t>
+          <t>44059; 50720</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20673; 26503</t>
+          <t>20672; 26401</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>104330; 116865</t>
+          <t>104265; 116904</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>123240; 136995</t>
+          <t>123809; 137067</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66727; 77154</t>
+          <t>65771; 77107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37186; 43886</t>
+          <t>36607; 43906</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37432; 44944</t>
+          <t>37215; 44950</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>76723; 78706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>98710; 105041</t>
+          <t>98819; 105041</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48761; 52442</t>
+          <t>49309; 52886</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>77756; 85612</t>
+          <t>77704; 85617</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>103144; 105119</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>113390; 122060</t>
+          <t>113567; 122037</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49950; 56633</t>
+          <t>50978; 56896</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>118162; 128839</t>
+          <t>118439; 128852</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>181833; 183825</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>216065; 225295</t>
+          <t>216120; 226007</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>100779; 108479</t>
+          <t>101070; 108620</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>123757; 136140</t>
+          <t>124364; 135867</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>145002; 159118</t>
+          <t>144527; 159231</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>133258; 145839</t>
+          <t>131971; 145731</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105251; 126885</t>
+          <t>105733; 127227</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>194079; 208478</t>
+          <t>193751; 208467</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>196328; 212987</t>
+          <t>195872; 213027</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>167565; 180699</t>
+          <t>168200; 180426</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>151521; 171349</t>
+          <t>152251; 170713</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>323672; 342574</t>
+          <t>322944; 342295</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>347015; 368645</t>
+          <t>348167; 369401</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>305590; 323587</t>
+          <t>304851; 323589</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>264677; 292322</t>
+          <t>263232; 293372</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>150793; 168014</t>
+          <t>149923; 167977</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>137511; 151116</t>
+          <t>137426; 151327</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>185873; 204699</t>
+          <t>186773; 205523</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>122244; 135380</t>
+          <t>122798; 135623</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>226835; 243289</t>
+          <t>227830; 243480</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>204608; 216978</t>
+          <t>204176; 216365</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>238659; 259006</t>
+          <t>239018; 259388</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>178207; 189354</t>
+          <t>176930; 188852</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>384523; 408038</t>
+          <t>385301; 408103</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>345879; 365145</t>
+          <t>347237; 365241</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>433070; 460236</t>
+          <t>433371; 461343</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>303969; 321677</t>
+          <t>304645; 321250</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>578628; 608216</t>
+          <t>576484; 607664</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>700171; 731094</t>
+          <t>700016; 730239</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>751017; 785293</t>
+          <t>753571; 786816</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>558659; 590780</t>
+          <t>557031; 591366</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>967160; 998057</t>
+          <t>964140; 997163</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1075256; 1103167</t>
+          <t>1074049; 1103455</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1053380; 1087911</t>
+          <t>1052613; 1087723</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>792725; 830583</t>
+          <t>792039; 831417</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1555133; 1600341</t>
+          <t>1552659; 1598206</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1784154; 1825881</t>
+          <t>1784283; 1825624</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1816540; 1865449</t>
+          <t>1815051; 1864231</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1360526; 1413011</t>
+          <t>1358544; 1410118</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P17G_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,3; 85,86</t>
+          <t>62,49; 86,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89,89; 100,0</t>
+          <t>88,87; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,35; 85,74</t>
+          <t>62,46; 84,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,2; 96,94</t>
+          <t>82,32; 97,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,56; 95,35</t>
+          <t>79,62; 95,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,75; 100,0</t>
+          <t>92,38; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,36; 97,09</t>
+          <t>86,88; 97,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,44; 93,2</t>
+          <t>82,77; 93,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76,88; 90,24</t>
+          <t>76,17; 90,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94,2; 99,38</t>
+          <t>93,21; 99,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79,42; 90,95</t>
+          <t>79,56; 90,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,16; 93,53</t>
+          <t>85,44; 93,79</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,48; 96,56</t>
+          <t>82,61; 96,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,25; 96,94</t>
+          <t>82,74; 96,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,62; 99,02</t>
+          <t>88,24; 98,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81,39; 95,78</t>
+          <t>80,6; 95,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,39; 95,27</t>
+          <t>84,7; 94,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,17; 98,01</t>
+          <t>90,97; 98,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,12; 98,8</t>
+          <t>93,02; 98,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,1; 95,52</t>
+          <t>86,08; 95,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,11; 94,48</t>
+          <t>86,19; 94,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89,11; 96,42</t>
+          <t>89,82; 96,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92,62; 97,93</t>
+          <t>93,35; 97,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>85,95; 94,68</t>
+          <t>86,38; 94,95</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,77; 98,24</t>
+          <t>81,42; 98,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,7; 97,74</t>
+          <t>86,87; 97,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,6; 95,56</t>
+          <t>81,6; 95,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80,65; 96,37</t>
+          <t>82,43; 96,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90,5; 99,01</t>
+          <t>90,52; 99,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,34; 99,28</t>
+          <t>90,52; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,13; 98,11</t>
+          <t>88,6; 98,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,66; 95,17</t>
+          <t>84,7; 95,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,39; 97,86</t>
+          <t>90,37; 97,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,84; 97,97</t>
+          <t>91,63; 97,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88,38; 95,87</t>
+          <t>88,31; 95,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>86,44; 94,7</t>
+          <t>86,96; 94,99</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,81; 98,35</t>
+          <t>85,87; 98,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,44; 95,63</t>
+          <t>77,75; 95,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,34; 98,84</t>
+          <t>87,57; 98,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79,17; 95,05</t>
+          <t>79,84; 94,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,11; 97,64</t>
+          <t>89,63; 97,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,33; 99,13</t>
+          <t>91,62; 99,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,37; 94,03</t>
+          <t>82,26; 94,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>88,24; 98,49</t>
+          <t>84,73; 95,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,67; 97,24</t>
+          <t>90,68; 97,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88,48; 96,75</t>
+          <t>88,53; 97,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86,5; 95,13</t>
+          <t>86,98; 95,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,87; 97,39</t>
+          <t>85,38; 93,83</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>81,59; 97,92</t>
+          <t>81,51; 97,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,75; 96,37</t>
+          <t>78,31; 96,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,43; 96,49</t>
+          <t>65,32; 94,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77,89; 100,0</t>
+          <t>76,48; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,74; 98,58</t>
+          <t>85,61; 97,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,67; 97,81</t>
+          <t>87,29; 97,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,87; 100,0</t>
+          <t>87,13; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,11; 93,37</t>
+          <t>71,31; 94,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86,28; 96,74</t>
+          <t>86,92; 96,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86,56; 95,83</t>
+          <t>86,69; 95,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82,32; 96,51</t>
+          <t>82,58; 96,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>78,69; 94,38</t>
+          <t>78,71; 94,61</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>81,11; 97,97</t>
+          <t>80,23; 97,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94,08; 100,0</t>
+          <t>94,02; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93,24; 100,0</t>
+          <t>93,02; 99,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>89,77; 98,91</t>
+          <t>89,87; 98,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,33; 99,21</t>
+          <t>92,24; 99,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>87,31; 97,45</t>
+          <t>86,73; 97,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89,42; 97,29</t>
+          <t>90,03; 97,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94,77; 99,11</t>
+          <t>94,79; 99,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>90,83; 97,62</t>
+          <t>91,14; 97,72</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>87,89; 96,02</t>
+          <t>87,53; 95,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,53; 95,33</t>
+          <t>86,47; 95,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,96; 97,14</t>
+          <t>86,79; 96,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74,17; 89,25</t>
+          <t>74,58; 88,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,09; 96,93</t>
+          <t>89,77; 96,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,54; 96,29</t>
+          <t>89,01; 96,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,73; 97,32</t>
+          <t>90,73; 97,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>77,76; 87,19</t>
+          <t>79,01; 88,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>90,57; 96,0</t>
+          <t>90,55; 95,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89,68; 95,14</t>
+          <t>89,95; 95,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90,89; 96,47</t>
+          <t>91,54; 96,58</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,8; 86,71</t>
+          <t>79,3; 87,16</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>83,65; 93,72</t>
+          <t>84,5; 93,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88,4; 97,34</t>
+          <t>88,43; 97,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,48; 92,97</t>
+          <t>84,32; 92,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86,67; 95,73</t>
+          <t>86,38; 95,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,5; 96,72</t>
+          <t>90,57; 96,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,74; 98,27</t>
+          <t>92,37; 98,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,47; 94,92</t>
+          <t>87,27; 94,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,01; 96,08</t>
+          <t>89,68; 95,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>89,4; 94,69</t>
+          <t>89,34; 94,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92,44; 97,24</t>
+          <t>92,73; 97,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87,67; 93,33</t>
+          <t>87,51; 93,24</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>90,07; 94,98</t>
+          <t>90,17; 95,22</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>87,9; 92,66</t>
+          <t>87,93; 92,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>91,05; 94,98</t>
+          <t>91,06; 95,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89,31; 93,25</t>
+          <t>88,97; 93,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86,85; 92,21</t>
+          <t>86,55; 91,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>91,97; 95,12</t>
+          <t>92,06; 95,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>94,5; 97,09</t>
+          <t>94,59; 97,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>92,14; 95,21</t>
+          <t>92,32; 95,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>88,34; 92,73</t>
+          <t>88,17; 91,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>91,11; 93,78</t>
+          <t>91,35; 93,88</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93,64; 95,81</t>
+          <t>93,64; 95,84</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91,38; 93,86</t>
+          <t>91,39; 93,85</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>88,34; 91,69</t>
+          <t>88,18; 91,02</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64404</t>
+          <t>59389</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66360</t>
+          <t>72593</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>130764</t>
+          <t>131981</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31274; 42425</t>
+          <t>30876; 42765</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55522; 61764</t>
+          <t>54887; 61764</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43551; 58942</t>
+          <t>42938; 58415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56999; 68049</t>
+          <t>53668; 63333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53326; 63115</t>
+          <t>52702; 63336</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87892; 94762</t>
+          <t>87539; 94762</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80915; 90975</t>
+          <t>81406; 90906</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61287; 70136</t>
+          <t>67358; 76117</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88870; 104318</t>
+          <t>88054; 104325</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>147440; 155548</t>
+          <t>145902; 155500</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129015; 147743</t>
+          <t>129240; 147703</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>122409; 136039</t>
+          <t>125237; 137471</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74205</t>
+          <t>76558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>88679</t>
+          <t>93318</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>162884</t>
+          <t>169875</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73458; 85997</t>
+          <t>73576; 86026</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85310; 100547</t>
+          <t>85824; 99812</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97172; 108574</t>
+          <t>96750; 107741</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66937; 78767</t>
+          <t>68421; 81226</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>111605; 125990</t>
+          <t>112014; 125440</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>140150; 152331</t>
+          <t>141394; 152370</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>167324; 177537</t>
+          <t>167155; 176700</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82247; 92325</t>
+          <t>87220; 97200</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>190565; 209094</t>
+          <t>190752; 208931</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>230912; 249864</t>
+          <t>232750; 250045</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>267981; 283348</t>
+          <t>270098; 283336</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>153765; 169375</t>
+          <t>160841; 176810</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57589</t>
+          <t>58492</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68994</t>
+          <t>71396</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>126583</t>
+          <t>129888</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45144; 53582</t>
+          <t>44407; 53587</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>69590; 78459</t>
+          <t>69734; 78422</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59186; 69314</t>
+          <t>59188; 69012</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51053; 61007</t>
+          <t>52797; 61568</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>90966; 99516</t>
+          <t>90982; 99531</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>125697; 138134</t>
+          <t>125942; 139135</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91367; 100575</t>
+          <t>90818; 100602</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64154; 72119</t>
+          <t>66286; 74578</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>140150; 151742</t>
+          <t>140119; 151409</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>201490; 214956</t>
+          <t>201031; 214738</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154693; 167801</t>
+          <t>154569; 167660</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>120233; 131710</t>
+          <t>123753; 135176</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62704</t>
+          <t>74772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>160392</t>
+          <t>103479</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>223096</t>
+          <t>178251</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44164; 50617</t>
+          <t>44196; 50578</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54138; 66856</t>
+          <t>54356; 66876</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76480; 86551</t>
+          <t>76685; 86544</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55631; 66786</t>
+          <t>67084; 79634</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106858; 117091</t>
+          <t>107490; 117107</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>101249; 108704</t>
+          <t>100469; 108701</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>110522; 126178</t>
+          <t>110385; 127394</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>149880; 167274</t>
+          <t>96022; 107910</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>155394; 166660</t>
+          <t>155420; 166729</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>158873; 173731</t>
+          <t>158961; 174307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>191811; 210955</t>
+          <t>192873; 210664</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>210989; 233841</t>
+          <t>168512; 185188</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>25439</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41299</t>
+          <t>43414</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36486; 43785</t>
+          <t>36448; 43790</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40422; 50107</t>
+          <t>40713; 50008</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18215; 28153</t>
+          <t>19058; 27560</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14210; 18243</t>
+          <t>14907; 19490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>64509; 75041</t>
+          <t>65171; 74560</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78903; 89047</t>
+          <t>79470; 88948</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44059; 50720</t>
+          <t>44192; 50720</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20672; 26401</t>
+          <t>21069; 27826</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>104265; 116904</t>
+          <t>105037; 116951</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>123809; 137067</t>
+          <t>123988; 137010</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65771; 77107</t>
+          <t>65981; 77129</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36607; 43906</t>
+          <t>38596; 46396</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51445</t>
+          <t>49710</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>54453</t>
+          <t>55791</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>105898</t>
+          <t>105501</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37215; 44950</t>
+          <t>36811; 44906</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3259,17 +3259,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>98819; 105041</t>
+          <t>98756; 105041</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49309; 52886</t>
+          <t>47578; 50716</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>77704; 85617</t>
+          <t>77795; 85588</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3279,17 +3279,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>113567; 122037</t>
+          <t>113457; 122060</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50978; 56896</t>
+          <t>51755; 58020</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>118439; 128852</t>
+          <t>119246; 128718</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>216120; 226007</t>
+          <t>216167; 226076</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>101070; 108620</t>
+          <t>101008; 108295</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117828</t>
+          <t>134991</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>161995</t>
+          <t>203746</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>279823</t>
+          <t>338738</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>124364; 135867</t>
+          <t>123850; 135772</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>144527; 159231</t>
+          <t>144435; 159378</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>131971; 145731</t>
+          <t>130204; 145475</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105733; 127227</t>
+          <t>121484; 144389</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>193751; 208467</t>
+          <t>193067; 208509</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>195872; 213027</t>
+          <t>196916; 212512</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>168200; 180426</t>
+          <t>168207; 181111</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>152251; 170713</t>
+          <t>191113; 213014</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>322944; 342295</t>
+          <t>322845; 341412</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>348167; 369401</t>
+          <t>349241; 369310</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>304851; 323589</t>
+          <t>307037; 323952</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>263232; 293372</t>
+          <t>321021; 352824</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130148</t>
+          <t>146113</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>184021</t>
+          <t>207075</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>314169</t>
+          <t>353189</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>149923; 167977</t>
+          <t>151454; 168132</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>137426; 151327</t>
+          <t>137465; 151451</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>186773; 205523</t>
+          <t>186409; 205397</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>122798; 135623</t>
+          <t>137285; 151814</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>227830; 243480</t>
+          <t>228003; 243120</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>204176; 216365</t>
+          <t>203372; 217010</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>239018; 259388</t>
+          <t>238470; 258876</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>176930; 188852</t>
+          <t>198372; 211944</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>385301; 408103</t>
+          <t>385041; 408576</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>347237; 365241</t>
+          <t>348334; 365619</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>433371; 461343</t>
+          <t>432588; 460947</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>304645; 321250</t>
+          <t>342773; 361957</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>575187</t>
+          <t>618001</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>809327</t>
+          <t>832836</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1384514</t>
+          <t>1450837</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>576484; 607664</t>
+          <t>576662; 607753</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>700016; 730239</t>
+          <t>700099; 731373</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>753571; 786816</t>
+          <t>750704; 786560</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>557031; 591366</t>
+          <t>597741; 634600</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>964140; 997163</t>
+          <t>965119; 997968</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1074049; 1103455</t>
+          <t>1075045; 1103089</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1052613; 1087723</t>
+          <t>1054730; 1088154</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>792039; 831417</t>
+          <t>817036; 848645</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1552659; 1598206</t>
+          <t>1556823; 1599828</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1784283; 1825624</t>
+          <t>1784250; 1826164</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1815051; 1864231</t>
+          <t>1815344; 1864046</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1358544; 1410118</t>
+          <t>1426064; 1471984</t>
         </is>
       </c>
     </row>
